--- a/samples/ss_krian3456_ingest.xlsx
+++ b/samples/ss_krian3456_ingest.xlsx
@@ -631,31 +631,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -702,27 +692,21 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -769,27 +753,21 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -836,27 +814,21 @@
       <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -903,19 +875,16 @@
       <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>1 IBT x 500 MVA; sementara sampai SUTET 500 kV siap</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -931,7 +900,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -960,35 +928,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>bus A1/A2 - B1/B2</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1017,23 +976,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>3x60 MVA</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1049,7 +1001,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1078,23 +1029,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>50/50/60 MVA</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1110,7 +1054,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1139,35 +1082,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>4x60 MVA + 50 MVAR</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1196,23 +1130,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>60 MVA (bay 3,4,9,10)</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1228,7 +1155,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1257,23 +1183,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>T/L bay Surabaya Barat single phi</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1289,7 +1208,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1336,19 +1254,16 @@
       <c r="J13" t="n">
         <v>2</v>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>kapasitas IBT tidak seimbang</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1364,7 +1279,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1393,23 +1307,16 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>single busbar; 30 MVA (bay 8)</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1425,7 +1332,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1454,23 +1360,16 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>single busbar; 30 MVA</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1486,7 +1385,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1515,35 +1413,26 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>60/40 MVA</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1572,35 +1461,26 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>20/12 MVA</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1629,35 +1509,26 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>30/30/10 MVA</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1686,35 +1557,26 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>30 MVA</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1821,7 +1683,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>SUTT Krian - Surabaya Barat</t>
@@ -1842,7 +1703,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -1856,8 +1716,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1874,13 +1732,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>SUTT Krian - Balongbendo</t>
@@ -1901,7 +1757,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -1915,8 +1770,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1933,7 +1786,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1964,7 +1816,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -1978,8 +1829,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1996,13 +1845,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>SUTT Krian - Bulubendo</t>
@@ -2023,7 +1870,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -2037,8 +1883,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2055,13 +1899,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>SUTT Krian - Driyorejo 150 kV</t>
@@ -2082,7 +1924,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -2096,8 +1937,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2114,7 +1953,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2145,7 +1983,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>1</v>
       </c>
@@ -2159,8 +1996,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2177,7 +2012,6 @@
           <t>Ya</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2208,7 +2042,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>1</v>
       </c>
@@ -2222,8 +2055,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2240,7 +2071,6 @@
           <t>Ya</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2271,7 +2101,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>1</v>
       </c>
@@ -2285,8 +2114,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2303,13 +2130,11 @@
           <t>Ya</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>SUTT 70 kV Driyorejo - Cikamia</t>
@@ -2330,7 +2155,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -2344,8 +2168,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2362,13 +2184,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>SUTT 70 kV Cikamia - Ajimoto</t>
@@ -2389,7 +2209,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>2</v>
       </c>
@@ -2403,8 +2222,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2421,13 +2238,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>SUTT 70 kV Cikamia - Tarik</t>
@@ -2448,7 +2263,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -2462,8 +2276,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2480,13 +2292,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>SUTT 70 kV Tarik - Bangun</t>
@@ -2507,7 +2317,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>2</v>
       </c>
@@ -2521,8 +2330,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2539,7 +2346,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2608,7 +2414,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[N-1] Dengan beroperasinya IBT 6 500/150 kV yang hanya sementara sampai kesiapan proyek SUTET 500 kV Krian-Waru, maka pembebanan IBT 500/150 kV Krian 3,4,5akan kembali tidak memenuhi kontingensi N-1 (kondisi sebelum beroperasi IBT 6 Krian). Atau jika konfigurasi Subsistem Krian 3456 dipolakan split menjadi 2 Subsistem (Mojokerto dan BKMS) maka kontingensi N-1 IBT pada Subsistem Mojokerto tidak terpenuhi. Bus section 150 kV GI Krian (Surabaya Barat) belum dapat beroperasi optimal</t>
+          <t>[N-1] Dengan beroperasinya IBT 6 500/150 kV yang hanya sementara sampai kesiapan proyek SUTET 500 kV Krian-Waru, maka pembebanan IBT 500/150 kV Krian 3,4,5 akan kembali tidak memenuhi kontingensi N-1 (kondisi sebelum beroperasi IBT 6 Krian). Atau jika konfigurasi Subsistem Krian 3456 dipolakan split menjadi 2 Subsistem (Mojokerto dan BKMS) maka kontingensi N-1 IBT pada Subsistem Mojokerto tidak terpenuhi. Bus section 150 kV GI Krian (Surabaya Barat) belum dapat beroperasi optimal</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2618,12 +2424,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1. Sudah terpasang OLS IBT Krian 3,4,5,6dengan tahapan 1-3 dan total target sebesar 578 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan hanya bisa dilaksanakan pada saat beban rendah</t>
+          <t>1. Sudah terpasang OLS IBT Krian 3,4,5,6 dengan tahapan 1-3 dan total target sebesar 578 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan hanya bisa dilaksanakan pada saat beban rendah</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Percepatan Rekonfigurasi dan Rerouting SUTT 150 kVBanaran- MojoagungmenjadiSUTT 150 kV Kediri-Mojoagung. (Berdasarkan RUPTL 2025 -2034, COD Tahun 2026). 2. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 -2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing- masing subsistem. 3. Pembangunan SUTET 500 kV Krian - Waru. (BerdasarkanRUPTL 2025 - 2034, CODTahun2025, MundurCOD 2028). 4. Percepatan pembangunan GITET 500 kV Ngoro dan line bay terkait. (Berdasarkan RUPTL 2025 -2034, COD Tahun 2027. JangkaPanjang: 5. Pembangunan PLTP Arjuna Welirang dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2032)</t>
+          <t>Jangka Pendek : 1. Percepatan Rekonfigurasi dan Rerouting SUTT 150 kV Banaran- Mojoagung menjadi SUTT 150 kV Kediri-Mojoagung. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing- masing subsistem. 3. Pembangunan SUTET 500 kV Krian - Waru. (Berdasarkan RUPTL 2025 - 2034, COD Tahun2025, Mundur COD 2028). 4. Percepatan pembangunan GITET 500 kV Ngoro dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027. Jangka Panjang: 5. Pembangunan PLTP Arjuna Welirang dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2032)</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2449,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[BELUM_DITETAPKAN] Pembebanan tidak seimbang karena konfigurasi single phi di GI Kasih Jatim T/L bay Surabaya Barat dan T/L Bay Cerme sudah berbeban diatas 60% apabila trip 1 sirkit SUTT 150 kV Kasih jatim-Cerme atau Kasih Jatim- Surabaya Barat maka terjadiOverload</t>
+          <t>[BELUM_DITETAPKAN] Pembebanan tidak seimbang karena konfigurasi single phi di GI Kasih Jatim T/L bay Surabaya Barat dan T/L Bay Cerme sudah berbeban diatas 60% apabila trip 1 sirkit SUTT 150 kV Kasih jatim-Cerme atau Kasih Jatim- Surabaya Barat maka terjadi Overload</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2653,12 +2459,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1. Pekerjaan dilakukan saat beban rendah. 2. Sudah terpasang OLS SUTT Surabaya Barat- Cerme dan Surabaya Barat-Kasih Jatimdan total target sebesar118 MW (Berdasarkan Deklarasi ROB Mei 2026)</t>
+          <t>1. Pekerjaan dilakukan saat beban rendah. 2. Sudah terpasang OLS SUTT Surabaya Barat- Cerme dan Surabaya Barat-Kasih Jatim dan total target sebesar 118 MW (Berdasarkan Deklarasi ROB Mei 2026)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 -2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note :Terkait dengan beroperasinya GITET 500 Usulan / Solusi kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing- masing subsistem. 2. Pembangunan SUTET 500 kV Krian - Waru. (BerdasarkanRUPTL 2025 - 2034, CODTahun2025, MundurCOD 2028). 3. Usulan normalisasi Double Phi di GI 150 kV Kasih Jatim untuk T/L bay Surabaya Barat dan T/L bay Cerme (sesuai kajian operasi dibutuhkan COD di 2026)</t>
+          <t>Jangka Pendek : 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note :Terkait dengan beroperasinya GITET 500 Usulan / Solusi kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing- masing subsistem. 2. Pembangunan SUTET 500 kV Krian - Waru. (Berdasarkan RUPTL 2025 - 2034, COD Tahun2025, Mundur COD 2028). 3. Usulan normalisasi Double Phi di GI 150 kV Kasih Jatim untuk T/L bay Surabaya Barat dan T/L bay Cerme (sesuai kajian operasi dibutuhkan COD di 2026)</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2484,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan tidak seimbang karena konfigurasi single phi GI Driyorejo T/L bay Surabaya Barat dan T/L Bay Babadan sudah berbeban &gt;70% karena flow beban lebih besar ke arah bay Driyorejo, sehingga tidak memenuhi kriteria N- 1. Terdapat Bottle Neck kapasitas MTU (CT) di GI Driyorejo masih kecil dibandingkan dengan kapasitas Konduktor dimana Inom PHT 1480 A Derating ke1000 A (mengikuti kemampuan CT) pada GI Driyorejo T/L bay Surabaya Barat, T/L bay Babadan</t>
+          <t>[N-1] Pembebanan tidak seimbang karena konfigurasi single phi GI Driyorejo T/L bay Surabaya Barat dan T/L Bay Babadan sudah berbeban &gt;70% karena flow beban lebih besar ke arah bay Driyorejo, sehingga tidak memenuhi kriteria N- 1. Terdapat Bottle Neck kapasitas MTU (CT) di GI Driyorejo masih kecil dibandingkan dengan kapasitas Konduktor dimana Inom PHT 1480 A Derating ke 1000 A (mengikuti kemampuan CT) pada GI Driyorejo T/L bay Surabaya Barat, T/L bay Babadan</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2688,12 +2494,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1. Pekerjaan dilakukan saat beban rendah. 2. Sudah terpasang OLS SUTT Surabaya Barat- Driyorejodan Surabaya Barat-Babadandengan total target sebesar 82 MW (Berdasarkan Deklarasi ROB Mei 2026)</t>
+          <t>1. Pekerjaan dilakukan saat beban rendah. 2. Sudah terpasang OLS SUTT Surabaya Barat- Driyorejo dan Surabaya Barat-Babadan dengan total target sebesar 82 MW (Berdasarkan Deklarasi ROB Mei 2026)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Penggantian dan uprating kapasitas MTU (CT) di GI 150 kV Driyorejo T/L bay Surabaya Barat dan T/L bay Babadan sesuai dengan Inom penghantar (1480 A). (COD dibutuhkan sistem di 2026). 2. Usulan normalisasi Double Phi GI Driyorejo T/L bay Surabaya Barat dan T/L bay Babadan (Sesuai kajian operasi dibutuhkan COD di 2026, estimasi COD 2027)</t>
+          <t>Jangka Pendek : 1. Penggantian dan uprating kapasitas MTU (CT) di GI 150 kV Driyorejo T/L bay Surabaya Barat dan T/L bay Babadan sesuai dengan Inom penghantar (1480 A). (COD dibutuhkan sistem di 2026). 2. Usulan normalisasi Double Phi GI Driyorejo T/L bay Surabaya Barat dan T/L bay Babadan (Sesuai kajian operasi dibutuhkan COD di 2026, estimasi COD 2027)</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2534,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Percepatan Rekonfigurasi dan Rerouting SUTT 150 kVBanaran- MojoagungmenjadiSUTT 150 kV Kediri-Mojoagung. (Berdasarkan RUPTL 2025 -2034, COD Tahun 2026). Usulan / Solusi 2. Usulan pemindahan level tegangan pelanggan KTT Dayasa terkait dari 70 kV ke 150 kV (diusulkan COD Tahun 2026). 3. Percepatan Pembangunan GITET 500 kV Ngoro dan line bay terkait. (Berdasarkan RUPTL 2025 -2034, COD Tahun 2027). 4. Usulan pembangunan GI 150 kV Tarik sebagai tambahan outlet GITET 500 kV Ngoro sebagai pengalihan beban trafo 70/20 kV GI 70 kV Tarik, usulan COD Bersamaan dengan GITET Ngoro Tahun 2027. JangkaPanjang: 5. Pembangunan PLTP Arjuna Welirang dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2032)</t>
+          <t>Jangka Pendek : 1. Percepatan Rekonfigurasi dan Rerouting SUTT 150 kV Banaran- Mojoagung menjadi SUTT 150 kV Kediri-Mojoagung. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). Usulan / Solusi 2. Usulan pemindahan level tegangan pelanggan KTT Dayasa terkait dari 70 kV ke 150 kV (diusulkan COD Tahun 2026). 3. Percepatan Pembangunan GITET 500 kV Ngoro dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 4. Usulan pembangunan GI 150 kV Tarik sebagai tambahan outlet GITET 500 kV Ngoro sebagai pengalihan beban trafo 70/20 kV GI 70 kV Tarik, usulan COD Bersamaan dengan GITET Ngoro Tahun 2027. Jangka Panjang: 5. Pembangunan PLTP Arjuna Welirang dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2032)</t>
         </is>
       </c>
     </row>
@@ -2748,22 +2554,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[N-1] Terjadi Ketidakseimbangan Pembebanan IBT 150/70 kV Driyorejo, yang diakibatkan oleh kapasitas IBT ( IBT-1 : 100 MVA, IBT - 2 : 50MVA)sehingga tidak memenuhi kriteria N- 1</t>
+          <t>[N-1] Terjadi Ketidakseimbangan Pembebanan IBT 150/70 kV Driyorejo, yang diakibatkan oleh kapasitas IBT ( IBT -1 : 100 MVA, IBT - 2 : 50MVA) sehingga tidak memenuhi kriteria N- 1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1. Overload padaIBT 150/70kV apabila trip salah satu IBT 150/70 kV tersebut. 2. Kesulitan dalam melakukan pemeliharaanIBT - 1 di hari kerja. 3. Terjadi overload saat KTT Operasi maksimum</t>
+          <t>1. Overload pada IBT 150/70kV apabila trip salah satu IBT 150/70 kV tersebut. 2. Kesulitan dalam melakukan pemeliharaan IBT - 1 di hari kerja. 3. Terjadi overload saat KTT Operasi maksimum</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1. Sudah terpasang OLS IBT 1,2 150/70 kV di GI Driyorejo dengan total target sebesar65 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan dilakukan saat beban rendah. 3. Beban GI Tarik, sebagian dipasok dari GI Sekarputih</t>
+          <t>1. Sudah terpasang OLS IBT 1,2 150/70 kV di GI Driyorejo dengan total target sebesar 65 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan dilakukan saat beban rendah. 3. Beban GI Tarik, sebagian dipasok dari GI Sekarputih</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Penggantian/relokasi IBT- 2 GI 150/70 kV Driyorejo dari 50 MVA menjadi 100 MVA. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. Usulan pemindahan level tegangan pelanggan KTT Dayasa terkait dari 70 kV ke 150 kV (diusulkan COD Tahun 2026). 3. Usulan pembangunan GI 150 kV Tarik sebagai tambahan outlet GITET 500 kV Ngoro sebagai pengalihan beban trafo 70/20 kV GI 70 kV Tarik, usulan COD Bersamaan dengan GITET Ngoro Tahun 2027</t>
+          <t>Jangka Pendek : 1. Penggantian/relokasi IBT- 2 GI 150/70 kV Driyorejo dari 50 MVA menjadi 100 MVA. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. Usulan pemindahan level tegangan pelanggan KTT Dayasa terkait dari 70 kV ke 150 kV (diusulkan COD Tahun 2026). 3. Usulan pembangunan GI 150 kV Tarik sebagai tambahan outlet GITET 500 kV Ngoro sebagai pengalihan beban trafo 70/20 kV GI 70 kV Tarik, usulan COD Bersamaan dengan GITET Ngoro Tahun 2027</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2604,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Usulan penambahan Busbar ke-2 (Double Busbar) beserta kopel Busbar di GI 70 kV Driyorejo (diusulkan COD masuk di 2026). Usulan / Solusi 2. Usulan pemindahan level tegangan pelanggan KTT Dayasa terkait dari 70 kV ke 150 kV (diusulkan COD Tahun 2026)</t>
+          <t>Jangka Pendek : 1. Usulan penambahan Busbar ke-2 (Double Busbar) beserta kopel Busbar di GI 70 kV Driyorejo (diusulkan COD masuk di 2026). Usulan / Solusi 2. Usulan pemindahan level tegangan pelanggan KTT Dayasa terkait dari 70 kV ke 150 kV (diusulkan COD Tahun 2026)</t>
         </is>
       </c>
     </row>
@@ -2823,17 +2629,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1. Overloadapabila trip 1 penghantar diruas tersebut. 2. Kesulitan dalam melakukan pemeliharaan di hari kerja</t>
+          <t>1. Overload apabila trip 1 penghantar diruas tersebut. 2. Kesulitan dalam melakukan pemeliharaan di hari kerja</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1. Sudah terpasang OLS SUTT 70 kV Miwon- Driyorejo dan Driyorejo-Tarik dengan total target sebesar48 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan dilakukan saat beban rendah</t>
+          <t>1. Sudah terpasang OLS SUTT 70 kV Miwon- Driyorejo dan Driyorejo-Tarik dengan total target sebesar 48 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan dilakukan saat beban rendah</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jangka Menengah: 1. Usulan baru normalisasi Double Phi di GI 70 kV Miwon T/L bay Driyorejo dan T/L bay Tarik (diusulkan COD Tahun 2026).Kajian operasi belum ada. 2. Usulan pemindahan level tegangan pelanggan KTT Dayasa terkait dari 70 kV ke 150 kV (diusulkan COD Tahun 2026). 3. Usulan Pembangunan GI 150 kV Tarik sebagai tambahan outlet GITET 500 kV Ngoro sebagai pengalihan beban trafo 70/20 kV GI 70 kV Tarik, usulan COD Bersamaan dengan GITET Ngoro Tahun 2027</t>
+          <t>Jangka Menengah : 1. Usulan baru normalisasi Double Phi di GI 70 kV Miwon T/L bay Driyorejo dan T/L bay Tarik (diusulkan COD Tahun 2026).Kajian operasi belum ada. 2. Usulan pemindahan level tegangan pelanggan KTT Dayasa terkait dari 70 kV ke 150 kV (diusulkan COD Tahun 2026). 3. Usulan Pembangunan GI 150 kV Tarik sebagai tambahan outlet GITET 500 kV Ngoro sebagai pengalihan beban trafo 70/20 kV GI 70 kV Tarik, usulan COD Bersamaan dengan GITET Ngoro Tahun 2027</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2674,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>JangkaPendek: Usulan penambahan Busbar ke-2(Double Busbar) beserta kopel Busbar di GI 70 kV Miwon (diusulkan COD masuk di 2026)</t>
+          <t>Jangka Pendek: Usulan penambahan Busbar ke-2 (Double Busbar) beserta kopel Busbar di GI 70 kV Miwon (diusulkan COD masuk di 2026)</t>
         </is>
       </c>
     </row>
